--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484675_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484675_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. ARIJA DE LA PENA</t>
+          <t>R. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6087</v>
+        <v>2.5344</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0324</v>
+        <v>1.0608</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5763</v>
+        <v>1.4736</v>
       </c>
       <c r="G2" t="n">
-        <v>3.5839</v>
+        <v>1.9068</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7247</v>
+        <v>1.6376</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8591</v>
+        <v>0.2691</v>
       </c>
       <c r="J2" t="n">
-        <v>4.6804</v>
+        <v>1.9514</v>
       </c>
       <c r="K2" t="n">
-        <v>2.6285</v>
+        <v>1.8423</v>
       </c>
       <c r="L2" t="n">
-        <v>2.0519</v>
+        <v>0.1091</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0965</v>
+        <v>-0.0446</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9038</v>
+        <v>-0.2047</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1928</v>
+        <v>0.16</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.7489</v>
+        <v>1.2828</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.9479</v>
+        <v>-0.3665</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1991</v>
+        <v>1.6493</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4413</v>
+        <v>-0.6552</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3341</v>
+        <v>-0.5241</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1072</v>
+        <v>-0.1311</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3324</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9658</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. DIAGNE</t>
+          <t>L. ORSINO BARCIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2048</v>
+        <v>2.5108</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8652</v>
+        <v>0.885</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3396</v>
+        <v>1.6258</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.6858</v>
+        <v>-1.5824</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.0187</v>
+        <v>-0.5151</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6671</v>
+        <v>-1.0673</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4761</v>
+        <v>-2.1542</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3094</v>
+        <v>-0.3501</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1667</v>
+        <v>-1.8041</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.1618</v>
+        <v>0.5718</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3281</v>
+        <v>-0.165</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8338</v>
+        <v>0.7368</v>
       </c>
       <c r="P3" t="n">
-        <v>1.4661</v>
+        <v>0.733</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.3665</v>
+        <v>-1.2828</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8326</v>
+        <v>2.0158</v>
       </c>
       <c r="S3" t="n">
-        <v>3.4245</v>
+        <v>-0.1188</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4337</v>
+        <v>0.1991</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9908</v>
+        <v>-0.3179</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>3.479</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3219</v>
+        <v>4.1229</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3219</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. NEBOT GARCIA</t>
+          <t>D. ARIJA DE LA PENA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0638</v>
+        <v>2.5007</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5736</v>
+        <v>1.4695</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4901</v>
+        <v>1.0312</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0041</v>
+        <v>3.5839</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8151</v>
+        <v>1.7247</v>
       </c>
       <c r="I4" t="n">
-        <v>0.189</v>
+        <v>1.8591</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9237</v>
+        <v>4.6804</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4397</v>
+        <v>2.6285</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.516</v>
+        <v>2.0519</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0804</v>
+        <v>-1.0965</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3754</v>
+        <v>-0.9038</v>
       </c>
       <c r="O4" t="n">
-        <v>0.705</v>
+        <v>-0.1928</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9163</v>
+        <v>-4.9479</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9163</v>
+        <v>2.1991</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0493</v>
+        <v>1.3333</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5558</v>
+        <v>0.7711</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5066000000000001</v>
+        <v>0.5622</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0104</v>
+        <v>0.3324</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0104</v>
+        <v>0.9658</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. HOLGADO CUELLAR</t>
+          <t>M. NEBOT GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9155</v>
+        <v>2.3307</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8134</v>
+        <v>0.6672</v>
       </c>
       <c r="F5" t="n">
-        <v>1.102</v>
+        <v>1.6635</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9068</v>
+        <v>2.0041</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6376</v>
+        <v>1.8151</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2691</v>
+        <v>0.189</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9514</v>
+        <v>0.9237</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8423</v>
+        <v>1.4397</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1091</v>
+        <v>-0.516</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0446</v>
+        <v>1.0804</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2047</v>
+        <v>0.3754</v>
       </c>
       <c r="O5" t="n">
-        <v>0.16</v>
+        <v>0.705</v>
       </c>
       <c r="P5" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.3665</v>
+        <v>-0.9163</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6493</v>
+        <v>0.9163</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2741</v>
+        <v>0.3162</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7715</v>
+        <v>0.6493</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5027</v>
+        <v>-0.3332</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.0104</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.0104</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. ARIJA DE LA PEÑA</t>
+          <t>P. ARNAU BELTRAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9005</v>
+        <v>2.0772</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9005</v>
+        <v>0.8988</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.1783</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9005</v>
+        <v>0.4536</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6502</v>
+        <v>0.8541</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2502</v>
+        <v>-0.4005</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9005</v>
+        <v>0.77</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6502</v>
+        <v>1.2663</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2502</v>
+        <v>-0.4963</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.3164</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.4122</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.0958</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.4661</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.7519</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.4012</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.3506</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. ARNAU BELTRAN</t>
+          <t>D. ARIJA DE LA PEÑA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3637</v>
+        <v>1.9005</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3101</v>
+        <v>1.9005</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6738</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4536</v>
+        <v>1.9005</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8541</v>
+        <v>0.6502</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4005</v>
+        <v>1.2502</v>
       </c>
       <c r="J7" t="n">
-        <v>0.77</v>
+        <v>1.9005</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2663</v>
+        <v>0.6502</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4963</v>
+        <v>1.2502</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3164</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4122</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0958</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4661</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0384</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8077</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8461</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. ORSINO BARCIA</t>
+          <t>E. DIAGNE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0982</v>
+        <v>1.3468</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.379</v>
+        <v>1.4779</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4772</v>
+        <v>-0.1311</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5824</v>
+        <v>-1.6858</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5151</v>
+        <v>-1.0187</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0673</v>
+        <v>-0.6671</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.1542</v>
+        <v>0.4761</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3501</v>
+        <v>0.3094</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.8041</v>
+        <v>0.1667</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5718</v>
+        <v>-2.1618</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.165</v>
+        <v>-1.3281</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7368</v>
+        <v>-0.8338</v>
       </c>
       <c r="P8" t="n">
-        <v>0.733</v>
+        <v>1.4661</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.2828</v>
+        <v>-0.3665</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0158</v>
+        <v>1.8326</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5314</v>
+        <v>1.5666</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0648</v>
+        <v>1.0464</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4665</v>
+        <v>0.5201</v>
       </c>
       <c r="V8" t="n">
-        <v>3.479</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>4.1229</v>
+        <v>0.3219</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6439</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5299</v>
+        <v>0.6509</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0187</v>
+        <v>1.1148</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4888</v>
+        <v>-0.464</v>
       </c>
       <c r="G9" t="n">
         <v>0.5134</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0165</v>
+        <v>0.1374</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0165</v>
+        <v>0.0413</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2611</v>
+        <v>0.4782</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0334</v>
+        <v>0.1589</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2945</v>
+        <v>0.3193</v>
       </c>
       <c r="G10" t="n">
         <v>0.3178</v>
@@ -1234,13 +1234,13 @@
         <v>0.3665</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4232</v>
+        <v>-0.2061</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0551</v>
+        <v>0.1373</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3681</v>
+        <v>-0.3433</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6028</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.985</v>
+        <v>-1.5865</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3823</v>
+        <v>0.9025</v>
       </c>
       <c r="G11" t="n">
         <v>-1.77</v>
@@ -1312,13 +1312,13 @@
         <v>1.4661</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4608</v>
+        <v>0.458</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6026</v>
+        <v>1.0012</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0634</v>
+        <v>-0.5432</v>
       </c>
       <c r="V11" t="n">
         <v>1.9109</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.4638</v>
+        <v>-6.2161</v>
       </c>
       <c r="E12" t="n">
         <v>-4.8877</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5761</v>
+        <v>-1.3284</v>
       </c>
       <c r="G12" t="n">
         <v>-2.7956</v>
@@ -1390,13 +1390,13 @@
         <v>0.9163</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8069</v>
+        <v>-0.5592</v>
       </c>
       <c r="T12" t="n">
         <v>-0.5875</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2195</v>
+        <v>0.0283</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5785</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.879599999999996</v>
+        <v>9.430100000000003</v>
       </c>
       <c r="E13" t="n">
-        <v>2.608600000000001</v>
+        <v>3.159199999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>6.270900000000001</v>
+        <v>6.2707</v>
       </c>
       <c r="G13" t="n">
         <v>2.8463</v>
@@ -1438,10 +1438,10 @@
         <v>3.647599999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8016000000000001</v>
+        <v>-0.8016000000000003</v>
       </c>
       <c r="J13" t="n">
-        <v>5.727099999999998</v>
+        <v>5.7271</v>
       </c>
       <c r="K13" t="n">
         <v>7.327299999999999</v>
@@ -1468,13 +1468,13 @@
         <v>12.8281</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4736</v>
+        <v>3.024099999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>2.6396</v>
+        <v>3.1902</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1662000000000001</v>
+        <v>-0.1662</v>
       </c>
       <c r="V13" t="n">
         <v>4.4761</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3189</v>
+        <v>3.673</v>
       </c>
       <c r="E14" t="n">
-        <v>2.476</v>
+        <v>2.3799</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8429</v>
+        <v>1.2932</v>
       </c>
       <c r="G14" t="n">
         <v>-0.3099</v>
@@ -1546,13 +1546,13 @@
         <v>1.4661</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.556</v>
+        <v>-0.2019</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1297</v>
+        <v>-0.2259</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4263</v>
+        <v>0.0239</v>
       </c>
       <c r="V14" t="n">
         <v>2.7188</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0433</v>
+        <v>2.7425</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.0338</v>
+        <v>-0.2646</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0771</v>
+        <v>3.0071</v>
       </c>
       <c r="G15" t="n">
         <v>1.3133</v>
@@ -1624,13 +1624,13 @@
         <v>2.0158</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.07630000000000001</v>
+        <v>0.6229</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6795</v>
+        <v>0.0898</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6031</v>
+        <v>0.5332</v>
       </c>
       <c r="V15" t="n">
         <v>0.6231</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. ROIG ARIÑO</t>
+          <t>G. GONZALEZ GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3005</v>
+        <v>2.2169</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3005</v>
+        <v>3.0227</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0.8058</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3005</v>
+        <v>2.5419</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3005</v>
+        <v>0.8813</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1.6606</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3005</v>
+        <v>3.3315</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3005</v>
+        <v>1.2538</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.0776</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-0.7896</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.3726</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0.417</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.1255</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.4838</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.4486</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.4486</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. GONZALEZ GARCIA</t>
+          <t>T. ROIG ARIÑO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.232</v>
+        <v>1.3005</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5419</v>
+        <v>1.3005</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3099</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5419</v>
+        <v>1.3005</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8813</v>
+        <v>1.3005</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6606</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3315</v>
+        <v>1.3005</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2538</v>
+        <v>1.3005</v>
       </c>
       <c r="L17" t="n">
-        <v>2.0776</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7896</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3726</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.417</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5943</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6063</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9879</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.4486</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.4486</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. DIAGO ROS</t>
+          <t>I. ALONSO QUINZA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0737</v>
+        <v>0.477</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5649</v>
+        <v>0.0929</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6385999999999999</v>
+        <v>0.3841</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2463</v>
+        <v>1.8772</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4801</v>
+        <v>0.3445</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2338</v>
+        <v>1.5327</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8627</v>
+        <v>3.3338</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.9044</v>
+        <v>1.929</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0417</v>
+        <v>1.4048</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6163999999999999</v>
+        <v>-1.4566</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4243</v>
+        <v>-1.5845</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1922</v>
+        <v>0.1279</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3665</v>
+        <v>-0.733</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3665</v>
+        <v>2.0158</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4499</v>
+        <v>-0.5405</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4276</v>
+        <v>-0.4921</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9777</v>
+        <v>-0.0485</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6439</v>
+        <v>-0.1267</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6439</v>
+        <v>-0.1267</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. VIVANCOS ORTIZ</t>
+          <t>J. CASADO SEGURA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3461</v>
+        <v>-0.6041</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9775</v>
+        <v>-0.5337</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6314</v>
+        <v>-0.0704</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7519</v>
+        <v>-0.1873</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2836</v>
+        <v>1.5246</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0355</v>
+        <v>-1.7118</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6725</v>
+        <v>0.6495</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0217</v>
+        <v>1.8482</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6509</v>
+        <v>-1.1987</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0793</v>
+        <v>-0.8368</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3053</v>
+        <v>-0.3237</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3846</v>
+        <v>-0.5131</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.6493</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0158</v>
+        <v>-1.0995</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3665</v>
+        <v>1.0995</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5514</v>
+        <v>-0.4169</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3658</v>
+        <v>-0.0837</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1856</v>
+        <v>-0.3332</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. ALONSO QUINZA</t>
+          <t>E. VIVANCOS ORTIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.6593</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3879</v>
+        <v>-1.266</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2235</v>
+        <v>0.6067</v>
       </c>
       <c r="G20" t="n">
-        <v>1.8772</v>
+        <v>0.7519</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3445</v>
+        <v>-0.2836</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5327</v>
+        <v>1.0355</v>
       </c>
       <c r="J20" t="n">
-        <v>3.3338</v>
+        <v>0.6725</v>
       </c>
       <c r="K20" t="n">
-        <v>1.929</v>
+        <v>0.0217</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4048</v>
+        <v>0.6509</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4566</v>
+        <v>0.0793</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5845</v>
+        <v>-0.3053</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1279</v>
+        <v>0.3846</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.733</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.7489</v>
+        <v>-2.0158</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0158</v>
+        <v>0.3665</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6289</v>
+        <v>0.2381</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9728</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6561</v>
+        <v>0.1608</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1267</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. CASADO SEGURA</t>
+          <t>A. DIAGO ROS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8416</v>
+        <v>-1.0003</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3414</v>
+        <v>-0.5889</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5002</v>
+        <v>-0.4113</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1873</v>
+        <v>-0.2463</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5246</v>
+        <v>-0.4801</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7118</v>
+        <v>0.2338</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6495</v>
+        <v>-0.8627</v>
       </c>
       <c r="K21" t="n">
-        <v>1.8482</v>
+        <v>-0.9044</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.1987</v>
+        <v>0.0417</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8368</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3237</v>
+        <v>0.4243</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5131</v>
+        <v>0.1922</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.3665</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0995</v>
+        <v>0.3665</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6544</v>
+        <v>-0.4766</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1086</v>
+        <v>0.2738</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.763</v>
+        <v>-0.7504</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. PARDO GALLENT</t>
+          <t>J. SAEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7067</v>
+        <v>-1.527</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4948</v>
+        <v>-2.3515</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2119</v>
+        <v>0.8244</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.613</v>
+        <v>-1.4619</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.004</v>
+        <v>-1.0547</v>
       </c>
       <c r="I22" t="n">
-        <v>0.391</v>
+        <v>-0.4072</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6418</v>
+        <v>-2.4141</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1675</v>
+        <v>-1.1737</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.4743</v>
+        <v>-1.2404</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0288</v>
+        <v>0.9522</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8365</v>
+        <v>0.119</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8653</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1833</v>
+        <v>0.733</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6493</v>
+        <v>0.733</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0005</v>
+        <v>-0.4762</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6576</v>
+        <v>0.0626</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3428</v>
+        <v>-0.5389</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.9109</v>
+        <v>-0.3219</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.2328</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. ALMONACID RUBIO</t>
+          <t>G. PARDO GALLENT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0739</v>
+        <v>-2.1117</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6797</v>
+        <v>-1.8794</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6059</v>
+        <v>-0.2323</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.7684</v>
+        <v>-0.613</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3581</v>
+        <v>-1.004</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.4103</v>
+        <v>0.391</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.5424</v>
+        <v>-0.6418</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6194</v>
+        <v>-0.1675</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.9231</v>
+        <v>-0.4743</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2259</v>
+        <v>0.0288</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7388</v>
+        <v>-0.8365</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5128</v>
+        <v>0.8653</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3665</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0995</v>
+        <v>-1.8326</v>
       </c>
       <c r="R23" t="n">
-        <v>0.733</v>
+        <v>1.6493</v>
       </c>
       <c r="S23" t="n">
-        <v>1.061</v>
+        <v>0.5954</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6403</v>
+        <v>0.273</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4207</v>
+        <v>0.3224</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.9109</v>
       </c>
       <c r="W23" t="n">
         <v>0.3219</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3219</v>
+        <v>-2.2328</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. SAEZ GONZALEZ</t>
+          <t>A. ALMONACID RUBIO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1535</v>
+        <v>-2.393</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9284</v>
+        <v>-2.7759</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7749</v>
+        <v>0.3829</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.4619</v>
+        <v>-2.7684</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0547</v>
+        <v>-1.3581</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4072</v>
+        <v>-1.4103</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.4141</v>
+        <v>-2.5424</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.1737</v>
+        <v>-0.6194</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.2404</v>
+        <v>-1.9231</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9522</v>
+        <v>-0.2259</v>
       </c>
       <c r="N24" t="n">
-        <v>0.119</v>
+        <v>-0.7388</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8332000000000001</v>
+        <v>0.5128</v>
       </c>
       <c r="P24" t="n">
-        <v>0.733</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="R24" t="n">
         <v>0.733</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1027</v>
+        <v>0.7419</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5143</v>
+        <v>0.5441</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5884</v>
+        <v>0.1978</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X24" t="n">
         <v>-0.3219</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>T. ROIG ARINO</t>
+          <t>J. VERGARA APARICIO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.0684</v>
+        <v>-4.137</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.8074</v>
+        <v>-0.0225</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.261</v>
+        <v>-4.1145</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.0171</v>
+        <v>-2.0271</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.8823</v>
+        <v>-0.7641</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1349</v>
+        <v>-1.263</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.698</v>
+        <v>0.2124</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.948</v>
+        <v>0.1609</v>
       </c>
       <c r="L25" t="n">
-        <v>0.25</v>
+        <v>0.0515</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.3192</v>
+        <v>-2.2395</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.9342</v>
+        <v>-0.925</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.3849</v>
+        <v>-1.3145</v>
       </c>
       <c r="P25" t="n">
+        <v>0.5498</v>
+      </c>
+      <c r="Q25" t="n">
         <v>-0.1833</v>
       </c>
-      <c r="Q25" t="n">
-        <v>-1.8326</v>
-      </c>
       <c r="R25" t="n">
-        <v>1.6493</v>
+        <v>0.733</v>
       </c>
       <c r="S25" t="n">
-        <v>1.4707</v>
+        <v>-0.6325</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4012</v>
+        <v>-0.0516</v>
       </c>
       <c r="U25" t="n">
-        <v>1.0695</v>
+        <v>-0.5809</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.3387</v>
+        <v>-2.0272</v>
       </c>
       <c r="W25" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.6606</v>
+        <v>-2.0272</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. VERGARA APARICIO</t>
+          <t>T. ROIG ARINO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.899</v>
+        <v>-4.9339</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.5032</v>
+        <v>-3.3843</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.3957</v>
+        <v>-1.5496</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.0271</v>
+        <v>-3.0171</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.7641</v>
+        <v>-2.8823</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.263</v>
+        <v>-0.1349</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2124</v>
+        <v>-1.698</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1609</v>
+        <v>-1.948</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0515</v>
+        <v>0.25</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.2395</v>
+        <v>-1.3192</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.925</v>
+        <v>-0.9342</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.3145</v>
+        <v>-0.3849</v>
       </c>
       <c r="P26" t="n">
-        <v>0.5498</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.1833</v>
+        <v>-1.8326</v>
       </c>
       <c r="R26" t="n">
-        <v>0.733</v>
+        <v>1.6493</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.3945</v>
+        <v>0.6052</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5324</v>
+        <v>-0.1757</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.8621</v>
+        <v>0.7809</v>
       </c>
       <c r="V26" t="n">
-        <v>-2.0272</v>
+        <v>-2.3387</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.0272</v>
+        <v>-2.6606</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-8.8796</v>
+        <v>-6.956399999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>-6.270799999999999</v>
+        <v>-6.270800000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.608599999999999</v>
+        <v>-0.6855000000000004</v>
       </c>
       <c r="G27" t="n">
         <v>-2.8462</v>
@@ -2530,16 +2530,16 @@
         <v>-3.6478</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8016000000000001</v>
+        <v>0.8016000000000005</v>
       </c>
       <c r="J27" t="n">
-        <v>2.880800000000001</v>
+        <v>2.8808</v>
       </c>
       <c r="K27" t="n">
         <v>3.679400000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.7988000000000003</v>
+        <v>-0.7988000000000002</v>
       </c>
       <c r="M27" t="n">
         <v>-5.7271</v>
@@ -2551,7 +2551,7 @@
         <v>1.6004</v>
       </c>
       <c r="P27" t="n">
-        <v>0.9163</v>
+        <v>0.9163000000000001</v>
       </c>
       <c r="Q27" t="n">
         <v>-12.8281</v>
@@ -2560,13 +2560,13 @@
         <v>13.7441</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.473600000000001</v>
+        <v>-0.5503999999999998</v>
       </c>
       <c r="T27" t="n">
         <v>0.1661000000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>-2.6398</v>
+        <v>-0.7166999999999998</v>
       </c>
       <c r="V27" t="n">
         <v>-4.476</v>
